--- a/IPVA.xlsx
+++ b/IPVA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pho3n\Downloads\calculo_parcela\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{173A9CEF-2110-4CD7-A8E0-2AAFBEDF91C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E74AE82-9292-44AC-AC72-403A2E006C7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5760" yWindow="5760" windowWidth="19176" windowHeight="19140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="26904" yWindow="5796" windowWidth="19176" windowHeight="19140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IPVA" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="133">
   <si>
     <t>UF</t>
   </si>
@@ -52,9 +52,6 @@
     <t xml:space="preserve">Minas Gerais </t>
   </si>
   <si>
-    <t xml:space="preserve">Espírito Santo </t>
-  </si>
-  <si>
     <t xml:space="preserve">Paraná </t>
   </si>
   <si>
@@ -419,6 +416,15 @@
   </si>
   <si>
     <t>Licenciamento</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>Ano 1</t>
+  </si>
+  <si>
+    <t>ISENTO</t>
   </si>
 </sst>
 </file>
@@ -428,7 +434,7 @@
   <numFmts count="1">
     <numFmt numFmtId="8" formatCode="&quot;R$&quot;\ #,##0.00;[Red]\-&quot;R$&quot;\ #,##0.00"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -439,6 +445,13 @@
     <font>
       <sz val="11"/>
       <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -467,10 +480,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -479,9 +493,12 @@
     <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Porcentagem" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -759,17 +776,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D28"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3.88671875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="7.77734375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.88671875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="22.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="68.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -777,125 +794,129 @@
         <v>1</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D1" s="3"/>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="F1" s="3"/>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="B2" s="1">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
       <c r="C2" s="4">
-        <v>174.08</v>
+        <v>200.25</v>
       </c>
       <c r="D2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="1">
-        <v>0.04</v>
+        <v>42</v>
+      </c>
+      <c r="B3" s="2">
+        <v>3.2500000000000001E-2</v>
       </c>
       <c r="C3" s="4">
-        <v>281.29000000000002</v>
+        <v>36.03</v>
       </c>
       <c r="D3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>4</v>
+        <v>48</v>
       </c>
       <c r="B4" s="1">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
       <c r="C4" s="4">
-        <v>35.619999999999997</v>
+        <v>122.88</v>
       </c>
       <c r="D4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="B5" s="1">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="C5" s="4">
-        <v>237.04</v>
+        <v>128.54</v>
       </c>
       <c r="D5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>33</v>
-      </c>
-      <c r="B6" s="2">
+        <v>39</v>
+      </c>
+      <c r="B6" s="1">
+        <v>0.03</v>
+      </c>
+      <c r="C6" s="4">
+        <v>173.5</v>
+      </c>
+      <c r="D6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B7" s="2">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="C6" s="4">
-        <v>90.94</v>
-      </c>
-      <c r="D6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>34</v>
-      </c>
-      <c r="B7" s="1">
-        <v>0.03</v>
-      </c>
       <c r="C7" s="4">
-        <v>109.27</v>
+        <v>220.45</v>
       </c>
       <c r="D7" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>35</v>
       </c>
-      <c r="B8" s="1">
-        <v>0.02</v>
+      <c r="B8" s="2">
+        <v>0.03</v>
       </c>
       <c r="C8" s="4">
-        <v>149.37</v>
+        <v>102</v>
       </c>
       <c r="D8" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
+        <v>31</v>
+      </c>
+      <c r="B9" s="1">
+        <v>0.02</v>
+      </c>
+      <c r="C9" s="4">
+        <v>237.04</v>
+      </c>
+      <c r="D9" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
         <v>36</v>
-      </c>
-      <c r="B9" s="2">
-        <v>3.5000000000000003E-2</v>
-      </c>
-      <c r="C9" s="4">
-        <v>102</v>
-      </c>
-      <c r="D9" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>37</v>
       </c>
       <c r="B10" s="2">
         <v>3.7499999999999999E-2</v>
@@ -904,116 +925,122 @@
         <v>274.61</v>
       </c>
       <c r="D10" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+      <c r="E10" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="B11" s="1">
         <v>0.03</v>
       </c>
       <c r="C11" s="4">
-        <v>140</v>
+        <v>157.33000000000001</v>
       </c>
       <c r="D11" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>39</v>
+        <v>4</v>
       </c>
       <c r="B12" s="1">
         <v>0.04</v>
       </c>
       <c r="C12" s="4">
+        <v>35.619999999999997</v>
+      </c>
+      <c r="D12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>38</v>
+      </c>
+      <c r="B13" s="7">
+        <v>4.4999999999999998E-2</v>
+      </c>
+      <c r="C13" s="4">
         <v>235.28</v>
       </c>
-      <c r="D12" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>40</v>
-      </c>
-      <c r="B13" s="1">
+      <c r="D13" t="s">
+        <v>14</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>37</v>
+      </c>
+      <c r="B14" s="1">
         <v>0.03</v>
       </c>
-      <c r="C13" s="4">
-        <v>173.5</v>
-      </c>
-      <c r="D13" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>41</v>
-      </c>
-      <c r="B14" s="2">
-        <v>3.5000000000000003E-2</v>
-      </c>
       <c r="C14" s="4">
-        <v>220.45</v>
+        <v>140</v>
       </c>
       <c r="D14" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="B15" s="2">
-        <v>2.4E-2</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="C15" s="4">
-        <v>119</v>
+        <v>288.08</v>
       </c>
       <c r="D15" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B16" s="2">
-        <v>3.2500000000000001E-2</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="C16" s="4">
-        <v>36.03</v>
+        <v>206.55</v>
       </c>
       <c r="D16" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>44</v>
-      </c>
-      <c r="B17" s="1">
-        <v>0.03</v>
+        <v>41</v>
+      </c>
+      <c r="B17" s="2">
+        <v>2.4E-2</v>
       </c>
       <c r="C17" s="4">
-        <v>157.33000000000001</v>
+        <v>119</v>
       </c>
       <c r="D17" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>45</v>
       </c>
-      <c r="B18" s="2">
-        <v>2.5000000000000001E-2</v>
+      <c r="B18" s="1">
+        <v>0.03</v>
       </c>
       <c r="C18" s="4">
-        <v>206.55</v>
+        <v>129.6</v>
       </c>
       <c r="D18" t="s">
         <v>21</v>
@@ -1021,146 +1048,150 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>46</v>
-      </c>
-      <c r="B19" s="1">
-        <v>0.03</v>
+        <v>32</v>
+      </c>
+      <c r="B19" s="2">
+        <v>1.9E-2</v>
       </c>
       <c r="C19" s="4">
-        <v>129.6</v>
+        <v>90.94</v>
       </c>
       <c r="D19" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>47</v>
+        <v>3</v>
       </c>
       <c r="B20" s="1">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="C20" s="4">
-        <v>100</v>
+        <v>281.29000000000002</v>
       </c>
       <c r="D20" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B21" s="1">
         <v>0.03</v>
       </c>
       <c r="C21" s="4">
-        <v>207.36</v>
+        <v>100</v>
       </c>
       <c r="D21" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B22" s="1">
         <v>0.03</v>
       </c>
       <c r="C22" s="4">
-        <v>122.88</v>
+        <v>220.41</v>
       </c>
       <c r="D22" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>50</v>
-      </c>
-      <c r="B23" s="2">
-        <v>2.5000000000000001E-2</v>
+        <v>53</v>
+      </c>
+      <c r="B23" s="1">
+        <v>0.03</v>
       </c>
       <c r="C23" s="4">
-        <v>288.08</v>
+        <v>110</v>
       </c>
       <c r="D23" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="B24" s="1">
         <v>0.02</v>
       </c>
       <c r="C24" s="4">
-        <v>200.25</v>
+        <v>109.27</v>
       </c>
       <c r="D24" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>52</v>
+        <v>34</v>
       </c>
       <c r="B25" s="1">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="C25" s="4">
-        <v>128.54</v>
+        <v>149.37</v>
       </c>
       <c r="D25" t="s">
-        <v>28</v>
+        <v>10</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="B26" s="1">
         <v>0.03</v>
       </c>
       <c r="C26" s="4">
-        <v>220.41</v>
+        <v>207.36</v>
       </c>
       <c r="D26" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>54</v>
+        <v>2</v>
       </c>
       <c r="B27" s="1">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="C27" s="4">
-        <v>110</v>
+        <v>174.08</v>
       </c>
       <c r="D27" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B28" s="1">
-        <v>0.02</v>
+        <v>3.5000000000000003E-2</v>
       </c>
       <c r="C28" s="4">
         <v>79.63</v>
       </c>
       <c r="D28" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D28">
+    <sortCondition ref="A1:A28"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1171,30 +1202,30 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B1" t="s">
         <v>56</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>57</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>58</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>59</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>60</v>
-      </c>
-      <c r="F1" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B2" t="s">
         <v>62</v>
-      </c>
-      <c r="B2" t="s">
-        <v>63</v>
       </c>
       <c r="C2" s="1">
         <v>0.04</v>
@@ -1206,12 +1237,12 @@
         <v>174.08</v>
       </c>
       <c r="F2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C3" s="1">
         <v>0.04</v>
@@ -1223,12 +1254,12 @@
         <v>281.29000000000002</v>
       </c>
       <c r="F3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C4" s="1">
         <v>0.04</v>
@@ -1240,12 +1271,12 @@
         <v>35.619999999999997</v>
       </c>
       <c r="F4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C5" s="1">
         <v>0.02</v>
@@ -1257,15 +1288,15 @@
         <v>237.04</v>
       </c>
       <c r="F5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
+        <v>70</v>
+      </c>
+      <c r="B6" t="s">
         <v>71</v>
-      </c>
-      <c r="B6" t="s">
-        <v>72</v>
       </c>
       <c r="C6" s="2">
         <v>3.5000000000000003E-2</v>
@@ -1277,12 +1308,12 @@
         <v>90.94</v>
       </c>
       <c r="F6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C7" s="1">
         <v>0.03</v>
@@ -1294,12 +1325,12 @@
         <v>109.27</v>
       </c>
       <c r="F7" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C8" s="1">
         <v>0.02</v>
@@ -1311,15 +1342,15 @@
         <v>149.37</v>
       </c>
       <c r="F8" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
+        <v>77</v>
+      </c>
+      <c r="B9" t="s">
         <v>78</v>
-      </c>
-      <c r="B9" t="s">
-        <v>79</v>
       </c>
       <c r="C9" s="2">
         <v>3.5000000000000003E-2</v>
@@ -1331,15 +1362,15 @@
         <v>102</v>
       </c>
       <c r="F9" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
+        <v>80</v>
+      </c>
+      <c r="C10" t="s">
         <v>81</v>
-      </c>
-      <c r="C10" t="s">
-        <v>82</v>
       </c>
       <c r="D10" s="1">
         <v>0.03</v>
@@ -1348,32 +1379,32 @@
         <v>251.25</v>
       </c>
       <c r="F10" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C11" s="1">
         <v>0.03</v>
       </c>
       <c r="D11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E11" s="4">
         <v>140</v>
       </c>
       <c r="F11" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
+        <v>86</v>
+      </c>
+      <c r="C12" t="s">
         <v>87</v>
-      </c>
-      <c r="C12" t="s">
-        <v>88</v>
       </c>
       <c r="D12" s="1">
         <v>0.02</v>
@@ -1382,18 +1413,18 @@
         <v>235.28</v>
       </c>
       <c r="F12" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
+        <v>89</v>
+      </c>
+      <c r="B13" t="s">
         <v>90</v>
       </c>
-      <c r="B13" t="s">
+      <c r="C13" t="s">
         <v>91</v>
-      </c>
-      <c r="C13" t="s">
-        <v>92</v>
       </c>
       <c r="D13" s="1">
         <v>0.01</v>
@@ -1402,49 +1433,49 @@
         <v>173.5</v>
       </c>
       <c r="F13" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
+        <v>93</v>
+      </c>
+      <c r="C14" t="s">
         <v>94</v>
       </c>
-      <c r="C14" t="s">
+      <c r="D14" t="s">
         <v>95</v>
-      </c>
-      <c r="D14" t="s">
-        <v>96</v>
       </c>
       <c r="E14" s="4">
         <v>220.45</v>
       </c>
       <c r="F14" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C15" s="2">
         <v>2.4E-2</v>
       </c>
       <c r="D15" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E15" s="4">
         <v>119</v>
       </c>
       <c r="F15" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B16" t="s">
+        <v>100</v>
+      </c>
+      <c r="C16" t="s">
         <v>101</v>
-      </c>
-      <c r="C16" t="s">
-        <v>102</v>
       </c>
       <c r="D16" s="1">
         <v>0.02</v>
@@ -1453,29 +1484,29 @@
         <v>36.03</v>
       </c>
       <c r="F16" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B17" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C17" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D17" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E17" s="4">
         <v>157.33000000000001</v>
       </c>
       <c r="F17" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B18" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C18" s="2">
         <v>2.5000000000000001E-2</v>
@@ -1487,15 +1518,15 @@
         <v>206.55</v>
       </c>
       <c r="F18" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B19" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C19" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D19" s="1">
         <v>0.02</v>
@@ -1504,12 +1535,12 @@
         <v>129.6</v>
       </c>
       <c r="F19" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B20" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C20" s="1">
         <v>0.03</v>
@@ -1521,15 +1552,15 @@
         <v>100</v>
       </c>
       <c r="F20" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B21" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C21" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D21" s="1">
         <v>0.02</v>
@@ -1538,18 +1569,18 @@
         <v>207.36</v>
       </c>
       <c r="F21" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
+        <v>113</v>
+      </c>
+      <c r="B22" t="s">
         <v>114</v>
       </c>
-      <c r="B22" t="s">
+      <c r="C22" t="s">
         <v>115</v>
-      </c>
-      <c r="C22" t="s">
-        <v>116</v>
       </c>
       <c r="D22" s="2">
         <v>1.4999999999999999E-2</v>
@@ -1558,12 +1589,12 @@
         <v>122.88</v>
       </c>
       <c r="F22" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B23" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C23" s="2">
         <v>2.5000000000000001E-2</v>
@@ -1575,12 +1606,12 @@
         <v>288.08</v>
       </c>
       <c r="F23" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B24" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C24" s="1">
         <v>0.02</v>
@@ -1592,12 +1623,12 @@
         <v>200.25</v>
       </c>
       <c r="F24" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B25" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C25" s="1">
         <v>0.03</v>
@@ -1609,12 +1640,12 @@
         <v>128.54</v>
       </c>
       <c r="F25" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B26" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C26" s="1">
         <v>0.03</v>
@@ -1626,12 +1657,12 @@
         <v>220.41</v>
       </c>
       <c r="F26" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B27" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C27" s="1">
         <v>0.03</v>
@@ -1643,12 +1674,12 @@
         <v>110</v>
       </c>
       <c r="F27" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B28" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C28" s="1">
         <v>0.02</v>
@@ -1660,7 +1691,7 @@
         <v>79.63</v>
       </c>
       <c r="F28" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
   </sheetData>

--- a/IPVA.xlsx
+++ b/IPVA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pho3n\Downloads\calculo_parcela\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E74AE82-9292-44AC-AC72-403A2E006C7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F465DFC0-2E52-4C94-9167-A2A5578F6760}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="26904" yWindow="5796" windowWidth="19176" windowHeight="19140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="134">
   <si>
     <t>UF</t>
   </si>
@@ -425,6 +425,9 @@
   </si>
   <si>
     <t>ISENTO</t>
+  </si>
+  <si>
+    <t>Isenção</t>
   </si>
 </sst>
 </file>
@@ -484,7 +487,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -493,7 +496,6 @@
     <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
@@ -800,7 +802,9 @@
       <c r="E1" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="F1" s="3"/>
+      <c r="F1" s="3" t="s">
+        <v>133</v>
+      </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
@@ -810,7 +814,7 @@
         <v>0.02</v>
       </c>
       <c r="C2" s="4">
-        <v>200.25</v>
+        <v>220.46</v>
       </c>
       <c r="D2" t="s">
         <v>26</v>
@@ -824,7 +828,7 @@
         <v>3.2500000000000001E-2</v>
       </c>
       <c r="C3" s="4">
-        <v>36.03</v>
+        <v>233.24</v>
       </c>
       <c r="D3" t="s">
         <v>18</v>
@@ -838,7 +842,7 @@
         <v>0.02</v>
       </c>
       <c r="C4" s="4">
-        <v>122.88</v>
+        <v>186.89</v>
       </c>
       <c r="D4" t="s">
         <v>24</v>
@@ -880,7 +884,7 @@
         <v>3.5000000000000003E-2</v>
       </c>
       <c r="C7" s="4">
-        <v>220.45</v>
+        <v>220.46</v>
       </c>
       <c r="D7" t="s">
         <v>16</v>
@@ -894,7 +898,7 @@
         <v>0.03</v>
       </c>
       <c r="C8" s="4">
-        <v>102</v>
+        <v>106.26</v>
       </c>
       <c r="D8" t="s">
         <v>11</v>
@@ -963,16 +967,16 @@
       <c r="A13" t="s">
         <v>38</v>
       </c>
-      <c r="B13" s="7">
+      <c r="B13" s="6">
         <v>4.4999999999999998E-2</v>
       </c>
       <c r="C13" s="4">
-        <v>235.28</v>
+        <v>237.64</v>
       </c>
       <c r="D13" t="s">
         <v>14</v>
       </c>
-      <c r="E13" s="6" t="s">
+      <c r="E13" t="s">
         <v>132</v>
       </c>
     </row>
@@ -984,7 +988,7 @@
         <v>0.03</v>
       </c>
       <c r="C14" s="4">
-        <v>140</v>
+        <v>300</v>
       </c>
       <c r="D14" t="s">
         <v>13</v>
@@ -998,7 +1002,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="C15" s="4">
-        <v>288.08</v>
+        <v>214.51</v>
       </c>
       <c r="D15" t="s">
         <v>25</v>
@@ -1012,7 +1016,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="C16" s="4">
-        <v>206.55</v>
+        <v>219.15</v>
       </c>
       <c r="D16" t="s">
         <v>20</v>
@@ -1026,7 +1030,7 @@
         <v>2.4E-2</v>
       </c>
       <c r="C17" s="4">
-        <v>119</v>
+        <v>158</v>
       </c>
       <c r="D17" t="s">
         <v>17</v>
@@ -1040,7 +1044,7 @@
         <v>0.03</v>
       </c>
       <c r="C18" s="4">
-        <v>129.6</v>
+        <v>168.5</v>
       </c>
       <c r="D18" t="s">
         <v>21</v>
@@ -1054,7 +1058,7 @@
         <v>1.9E-2</v>
       </c>
       <c r="C19" s="4">
-        <v>90.94</v>
+        <v>94.61</v>
       </c>
       <c r="D19" t="s">
         <v>8</v>
@@ -1068,7 +1072,7 @@
         <v>0.04</v>
       </c>
       <c r="C20" s="4">
-        <v>281.29000000000002</v>
+        <v>293.70999999999998</v>
       </c>
       <c r="D20" t="s">
         <v>6</v>
@@ -1082,7 +1086,7 @@
         <v>0.03</v>
       </c>
       <c r="C21" s="4">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="D21" t="s">
         <v>22</v>
@@ -1110,7 +1114,7 @@
         <v>0.03</v>
       </c>
       <c r="C23" s="4">
-        <v>110</v>
+        <v>139.37</v>
       </c>
       <c r="D23" t="s">
         <v>29</v>
@@ -1124,7 +1128,7 @@
         <v>0.02</v>
       </c>
       <c r="C24" s="4">
-        <v>109.27</v>
+        <v>114.19</v>
       </c>
       <c r="D24" t="s">
         <v>9</v>
@@ -1152,7 +1156,7 @@
         <v>0.03</v>
       </c>
       <c r="C26" s="4">
-        <v>207.36</v>
+        <v>150</v>
       </c>
       <c r="D26" t="s">
         <v>23</v>
